--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$97</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3572" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3536" uniqueCount="551">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -467,22 +467,6 @@
 </t>
   </si>
   <si>
-    <t>ServiceRequest.extension:Evidenzgraduierung</t>
-  </si>
-  <si>
-    <t>Evidenzgraduierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/StructureDefinition/mii-ex-seltene-empfehlung-evidenzgraduierung}
-</t>
-  </si>
-  <si>
-    <t>MII EX SE Empfehlung Evidenzgraduierung</t>
-  </si>
-  <si>
-    <t>Evidenzgraduierung der (einzelnen) Empfehlung</t>
-  </si>
-  <si>
     <t>ServiceRequest.extension:Publikation</t>
   </si>
   <si>
@@ -746,7 +730,7 @@
     <t>http://hl7.org/fhir/ValueSet/servicerequest-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:coding.system}
 </t>
   </si>
   <si>
@@ -869,6 +853,9 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/CodeSystem/mii-cs-seltene-therapieempfehlung-strategie</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -1024,6 +1011,9 @@
   </si>
   <si>
     <t>ServiceRequest.category:MVGenomSeqTherapieTyp.coding.system</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/CodeSystem/mii-cs-seltene-therapieempfehlung-typ</t>
   </si>
   <si>
     <t>ServiceRequest.category:MVGenomSeqTherapieTyp.coding.version</t>
@@ -2056,7 +2046,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN98"/>
+  <dimension ref="A1:AN97"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.83984375" customWidth="true" bestFit="true"/>
@@ -3258,7 +3248,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>89</v>
@@ -3354,18 +3344,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C12" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3375,25 +3363,29 @@
         <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I12" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I12" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="J12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
       </c>
@@ -3441,7 +3433,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3450,7 +3442,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>137</v>
@@ -3470,14 +3462,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3490,26 +3482,24 @@
         <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J13" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J13" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K13" t="s" s="2">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>80</v>
       </c>
@@ -3557,7 +3547,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3569,27 +3559,27 @@
         <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>80</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3612,16 +3602,16 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3671,7 +3661,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3686,24 +3676,24 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3726,16 +3716,16 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3785,7 +3775,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3800,10 +3790,10 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>80</v>
@@ -3821,7 +3811,7 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3840,17 +3830,15 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3914,10 +3902,10 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>80</v>
@@ -3928,14 +3916,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3954,13 +3942,13 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4011,7 +3999,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4026,10 +4014,10 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>80</v>
@@ -4040,21 +4028,21 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>80</v>
@@ -4066,16 +4054,20 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
       </c>
@@ -4123,13 +4115,13 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>80</v>
@@ -4138,10 +4130,10 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>80</v>
@@ -4150,48 +4142,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>162</v>
+        <v>108</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
       </c>
@@ -4215,13 +4205,13 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>80</v>
+        <v>203</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>80</v>
+        <v>204</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>80</v>
@@ -4239,10 +4229,10 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>88</v>
@@ -4254,24 +4244,24 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4297,13 +4287,13 @@
         <v>108</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4314,7 +4304,7 @@
         <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>80</v>
@@ -4329,31 +4319,31 @@
         <v>80</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="Z20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>88</v>
@@ -4368,24 +4358,24 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>214</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4396,30 +4386,32 @@
         <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>220</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4428,7 +4420,7 @@
         <v>80</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>80</v>
@@ -4443,37 +4435,37 @@
         <v>80</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="Y21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="Z21" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="AG21" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
@@ -4482,35 +4474,37 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>221</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>89</v>
@@ -4522,19 +4516,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4559,31 +4553,29 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>234</v>
+        <v>80</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4601,25 +4593,23 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4631,29 +4621,25 @@
         <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4677,11 +4663,13 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
@@ -4699,28 +4687,28 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>223</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>80</v>
@@ -4728,21 +4716,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4754,7 +4742,7 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>244</v>
+        <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>245</v>
@@ -4762,7 +4750,9 @@
       <c r="M24" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N24" s="2"/>
+      <c r="N24" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4799,31 +4789,31 @@
         <v>80</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
@@ -4840,21 +4830,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
@@ -4863,21 +4853,23 @@
         <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
       </c>
@@ -4913,19 +4905,19 @@
         <v>80</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4937,13 +4929,13 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>80</v>
@@ -4954,10 +4946,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4965,7 +4957,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>88</v>
@@ -4977,23 +4969,19 @@
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
@@ -5041,25 +5029,25 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
@@ -5070,21 +5058,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
@@ -5096,7 +5084,7 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>244</v>
+        <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>245</v>
@@ -5104,7 +5092,9 @@
       <c r="M27" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N27" s="2"/>
+      <c r="N27" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -5141,31 +5131,31 @@
         <v>80</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
@@ -5182,21 +5172,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -5205,21 +5195,23 @@
         <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
       </c>
@@ -5228,7 +5220,7 @@
         <v>80</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>80</v>
@@ -5255,37 +5247,37 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>80</v>
@@ -5296,10 +5288,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5307,7 +5299,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
@@ -5322,20 +5314,18 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>102</v>
+        <v>239</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
@@ -5383,7 +5373,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5401,7 +5391,7 @@
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>80</v>
@@ -5412,10 +5402,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5423,7 +5413,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>88</v>
@@ -5438,18 +5428,18 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>244</v>
+        <v>108</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -5497,7 +5487,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5515,7 +5505,7 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
@@ -5526,10 +5516,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5537,7 +5527,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
@@ -5552,17 +5542,17 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5611,7 +5601,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5629,7 +5619,7 @@
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
@@ -5640,10 +5630,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5666,17 +5656,19 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5725,7 +5717,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5743,7 +5735,7 @@
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
@@ -5754,10 +5746,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5780,19 +5772,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>298</v>
+        <v>239</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5841,7 +5833,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5859,7 +5851,7 @@
         <v>80</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>80</v>
@@ -5868,14 +5860,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>80</v>
       </c>
@@ -5887,7 +5881,7 @@
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>80</v>
@@ -5896,19 +5890,19 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>310</v>
+        <v>224</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5933,13 +5927,11 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>80</v>
+        <v>314</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -5957,13 +5949,13 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>311</v>
+        <v>219</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
@@ -5975,25 +5967,23 @@
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>312</v>
+        <v>230</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>80</v>
       </c>
@@ -6005,29 +5995,25 @@
         <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>315</v>
+        <v>240</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
@@ -6051,11 +6037,13 @@
         <v>80</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>80</v>
@@ -6073,28 +6061,28 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>235</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>223</v>
+        <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -6102,21 +6090,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -6128,7 +6116,7 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>244</v>
+        <v>131</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>245</v>
@@ -6136,7 +6124,9 @@
       <c r="M36" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N36" s="2"/>
+      <c r="N36" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6173,31 +6163,31 @@
         <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
@@ -6214,21 +6204,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
@@ -6237,21 +6227,23 @@
         <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6287,19 +6279,19 @@
         <v>80</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6311,13 +6303,13 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>80</v>
@@ -6328,10 +6320,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6339,7 +6331,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
@@ -6351,23 +6343,19 @@
         <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6415,25 +6403,25 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
@@ -6444,21 +6432,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
@@ -6470,7 +6458,7 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>244</v>
+        <v>131</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>245</v>
@@ -6478,7 +6466,9 @@
       <c r="M39" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N39" s="2"/>
+      <c r="N39" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6515,31 +6505,31 @@
         <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -6556,21 +6546,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6579,21 +6569,23 @@
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
@@ -6602,7 +6594,7 @@
         <v>80</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>80</v>
+        <v>321</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>80</v>
@@ -6629,37 +6621,37 @@
         <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
@@ -6670,10 +6662,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6681,7 +6673,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>88</v>
@@ -6696,20 +6688,18 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>102</v>
+        <v>239</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
       </c>
@@ -6757,7 +6747,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6775,7 +6765,7 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
@@ -6786,10 +6776,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6797,7 +6787,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>88</v>
@@ -6812,18 +6802,18 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>244</v>
+        <v>108</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
@@ -6871,7 +6861,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6889,7 +6879,7 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
@@ -6900,10 +6890,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6911,7 +6901,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>88</v>
@@ -6926,17 +6916,17 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -6985,7 +6975,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7003,7 +6993,7 @@
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
@@ -7014,10 +7004,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7040,17 +7030,19 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7099,7 +7091,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7117,7 +7109,7 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -7128,10 +7120,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7154,19 +7146,19 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>298</v>
+        <v>239</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7215,7 +7207,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7233,7 +7225,7 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
@@ -7242,12 +7234,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7261,7 +7253,7 @@
         <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>80</v>
@@ -7270,24 +7262,22 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>244</v>
+        <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q46" s="2"/>
+      <c r="Q46" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="R46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7307,13 +7297,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>80</v>
+        <v>203</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7331,7 +7321,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7346,24 +7336,24 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>80</v>
+        <v>333</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>80</v>
+        <v>335</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7377,30 +7367,34 @@
         <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I47" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>108</v>
+        <v>294</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q47" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="R47" t="s" s="2">
         <v>80</v>
@@ -7421,13 +7415,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>334</v>
+        <v>80</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7445,7 +7439,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7460,110 +7454,106 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>338</v>
+        <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>80</v>
+        <v>344</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>298</v>
+        <v>220</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O48" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q48" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="R48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7578,57 +7568,55 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>80</v>
+        <v>351</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>347</v>
+        <v>80</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>348</v>
+        <v>240</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7653,13 +7641,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7677,7 +7665,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>346</v>
+        <v>242</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7689,38 +7677,38 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>353</v>
+        <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>354</v>
+        <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>355</v>
+        <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>356</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>80</v>
@@ -7732,7 +7720,7 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>244</v>
+        <v>131</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>245</v>
@@ -7740,7 +7728,9 @@
       <c r="M50" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N50" s="2"/>
+      <c r="N50" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7777,31 +7767,31 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
@@ -7818,14 +7808,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7841,21 +7831,23 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
@@ -7891,11 +7883,9 @@
         <v>80</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>80</v>
       </c>
@@ -7903,7 +7893,7 @@
         <v>135</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7915,13 +7905,13 @@
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>80</v>
@@ -7930,14 +7920,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="B52" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>80</v>
       </c>
@@ -7946,10 +7938,10 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
@@ -7958,19 +7950,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7995,29 +7987,29 @@
         <v>80</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>80</v>
+        <v>361</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AC52" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8035,7 +8027,7 @@
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
@@ -8044,16 +8036,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8065,29 +8055,25 @@
         <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8111,11 +8097,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>364</v>
+        <v>80</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8133,25 +8121,25 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
@@ -8162,21 +8150,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>80</v>
@@ -8188,7 +8176,7 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>244</v>
+        <v>131</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>245</v>
@@ -8196,7 +8184,9 @@
       <c r="M54" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N54" s="2"/>
+      <c r="N54" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8233,31 +8223,31 @@
         <v>80</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8274,21 +8264,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>80</v>
@@ -8297,21 +8287,23 @@
         <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8320,7 +8312,7 @@
         <v>80</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>80</v>
+        <v>368</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>80</v>
@@ -8347,37 +8339,37 @@
         <v>80</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8399,7 +8391,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>88</v>
@@ -8414,20 +8406,18 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>102</v>
+        <v>239</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8436,7 +8426,7 @@
         <v>80</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>371</v>
+        <v>80</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>80</v>
@@ -8475,7 +8465,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8493,7 +8483,7 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
@@ -8504,10 +8494,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8530,18 +8520,18 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>244</v>
+        <v>108</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8589,7 +8579,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8607,7 +8597,7 @@
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
@@ -8618,10 +8608,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8644,17 +8634,17 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8703,7 +8693,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8721,7 +8711,7 @@
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
@@ -8732,10 +8722,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8758,17 +8748,19 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -8817,7 +8809,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8835,7 +8827,7 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
@@ -8844,14 +8836,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C60" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="B60" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>80</v>
       </c>
@@ -8863,7 +8857,7 @@
         <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>80</v>
@@ -8872,19 +8866,19 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>298</v>
+        <v>251</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>301</v>
+        <v>254</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -8909,13 +8903,11 @@
         <v>80</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>80</v>
+        <v>379</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
@@ -8933,13 +8925,13 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
@@ -8951,7 +8943,7 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
@@ -8960,16 +8952,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>380</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>80</v>
       </c>
@@ -8981,29 +8971,25 @@
         <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -9027,11 +9013,13 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>382</v>
+        <v>80</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9049,25 +9037,25 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
@@ -9078,21 +9066,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>80</v>
@@ -9104,7 +9092,7 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>244</v>
+        <v>131</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>245</v>
@@ -9112,7 +9100,9 @@
       <c r="M62" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N62" s="2"/>
+      <c r="N62" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9149,31 +9139,31 @@
         <v>80</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
@@ -9190,21 +9180,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>80</v>
@@ -9213,21 +9203,23 @@
         <v>80</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
       </c>
@@ -9236,7 +9228,7 @@
         <v>80</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>80</v>
+        <v>383</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>80</v>
@@ -9263,37 +9255,37 @@
         <v>80</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
@@ -9304,7 +9296,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>370</v>
@@ -9315,7 +9307,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>88</v>
@@ -9330,20 +9322,18 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>102</v>
+        <v>239</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
@@ -9352,7 +9342,7 @@
         <v>80</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>386</v>
+        <v>80</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>80</v>
@@ -9391,7 +9381,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9409,7 +9399,7 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
@@ -9420,10 +9410,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9446,18 +9436,18 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>244</v>
+        <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
       </c>
@@ -9505,7 +9495,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9523,7 +9513,7 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
@@ -9534,10 +9524,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9560,17 +9550,17 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9619,7 +9609,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9637,7 +9627,7 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -9648,10 +9638,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9674,17 +9664,19 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O67" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -9733,7 +9725,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9751,7 +9743,7 @@
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
@@ -9760,14 +9752,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>80</v>
       </c>
@@ -9779,7 +9773,7 @@
         <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>80</v>
@@ -9788,19 +9782,19 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>298</v>
+        <v>251</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>301</v>
+        <v>254</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -9849,13 +9843,13 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>80</v>
@@ -9867,7 +9861,7 @@
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>80</v>
@@ -9876,16 +9870,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>80</v>
       </c>
@@ -9897,29 +9889,25 @@
         <v>88</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
@@ -9967,25 +9955,25 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>80</v>
@@ -9996,21 +9984,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>80</v>
@@ -10022,7 +10010,7 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>244</v>
+        <v>131</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>245</v>
@@ -10030,7 +10018,9 @@
       <c r="M70" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N70" s="2"/>
+      <c r="N70" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10067,31 +10057,31 @@
         <v>80</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>80</v>
@@ -10108,21 +10098,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>80</v>
@@ -10131,21 +10121,23 @@
         <v>80</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
       </c>
@@ -10154,7 +10146,7 @@
         <v>80</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>80</v>
+        <v>393</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>80</v>
@@ -10181,37 +10173,37 @@
         <v>80</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>80</v>
@@ -10222,7 +10214,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>370</v>
@@ -10233,7 +10225,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>88</v>
@@ -10248,20 +10240,18 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>102</v>
+        <v>239</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>80</v>
       </c>
@@ -10270,7 +10260,7 @@
         <v>80</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>396</v>
+        <v>80</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>80</v>
@@ -10309,7 +10299,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10327,7 +10317,7 @@
         <v>80</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>80</v>
@@ -10338,10 +10328,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10364,18 +10354,18 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>244</v>
+        <v>108</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
       </c>
@@ -10423,7 +10413,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10441,7 +10431,7 @@
         <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>80</v>
@@ -10452,10 +10442,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10478,17 +10468,17 @@
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -10537,7 +10527,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10555,7 +10545,7 @@
         <v>80</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>80</v>
@@ -10566,10 +10556,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10592,17 +10582,19 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O75" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -10651,7 +10643,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10669,7 +10661,7 @@
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>80</v>
@@ -10678,12 +10670,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10691,13 +10683,13 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>80</v>
@@ -10706,19 +10698,19 @@
         <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>298</v>
+        <v>239</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -10767,7 +10759,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10785,7 +10777,7 @@
         <v>80</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>80</v>
@@ -10794,26 +10786,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>80</v>
@@ -10822,20 +10814,18 @@
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>307</v>
+        <v>401</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>308</v>
+        <v>402</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>80</v>
       </c>
@@ -10859,13 +10849,13 @@
         <v>80</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>80</v>
+        <v>225</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>80</v>
+        <v>404</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>80</v>
+        <v>405</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -10883,16 +10873,16 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>311</v>
+        <v>399</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>80</v>
+        <v>406</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>100</v>
@@ -10901,32 +10891,32 @@
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>312</v>
+        <v>407</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>403</v>
+        <v>80</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>80</v>
@@ -10938,18 +10928,18 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>225</v>
+        <v>409</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
       </c>
@@ -10973,40 +10963,40 @@
         <v>80</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>407</v>
+        <v>80</v>
       </c>
       <c r="Z78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AA78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>100</v>
@@ -11015,21 +11005,21 @@
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>356</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11037,13 +11027,13 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>80</v>
@@ -11052,18 +11042,16 @@
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N79" s="2"/>
-      <c r="O79" t="s" s="2">
-        <v>415</v>
-      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>80</v>
       </c>
@@ -11111,10 +11099,10 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>88</v>
@@ -11126,32 +11114,32 @@
         <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>80</v>
+        <v>417</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>80</v>
+        <v>419</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>80</v>
+        <v>422</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>88</v>
@@ -11166,13 +11154,13 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11223,10 +11211,10 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>88</v>
@@ -11238,28 +11226,28 @@
         <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11278,13 +11266,13 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11335,7 +11323,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11350,28 +11338,28 @@
         <v>100</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>434</v>
+        <v>80</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11381,7 +11369,7 @@
         <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>80</v>
@@ -11390,13 +11378,13 @@
         <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11423,13 +11411,13 @@
         <v>80</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>80</v>
+        <v>225</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>80</v>
+        <v>443</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>80</v>
+        <v>444</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>80</v>
@@ -11447,7 +11435,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11462,28 +11450,28 @@
         <v>100</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>439</v>
+        <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>80</v>
+        <v>447</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11502,13 +11490,13 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11535,31 +11523,31 @@
         <v>80</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11574,28 +11562,28 @@
         <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>80</v>
+        <v>452</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>80</v>
+        <v>453</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11605,7 +11593,7 @@
         <v>88</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>80</v>
@@ -11614,15 +11602,17 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -11671,7 +11661,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11686,28 +11676,28 @@
         <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -11717,7 +11707,7 @@
         <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>80</v>
@@ -11726,16 +11716,16 @@
         <v>89</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>460</v>
+        <v>220</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11761,13 +11751,13 @@
         <v>80</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>80</v>
+        <v>225</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>80</v>
+        <v>471</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>80</v>
@@ -11785,7 +11775,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11800,38 +11790,38 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>467</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>80</v>
@@ -11840,16 +11830,16 @@
         <v>89</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>225</v>
+        <v>477</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11875,13 +11865,13 @@
         <v>80</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>474</v>
+        <v>80</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>80</v>
@@ -11899,13 +11889,13 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>80</v>
@@ -11914,28 +11904,28 @@
         <v>100</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>479</v>
+        <v>80</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -11945,7 +11935,7 @@
         <v>79</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>80</v>
@@ -11954,17 +11944,15 @@
         <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>480</v>
+        <v>220</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -11989,13 +11977,13 @@
         <v>80</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>80</v>
+        <v>225</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>80</v>
+        <v>486</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>80</v>
+        <v>487</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
@@ -12013,7 +12001,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12028,13 +12016,13 @@
         <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>484</v>
+        <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>485</v>
+        <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>80</v>
@@ -12042,10 +12030,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12068,13 +12056,13 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>225</v>
+        <v>489</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12101,13 +12089,13 @@
         <v>80</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>489</v>
+        <v>80</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -12125,7 +12113,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12146,13 +12134,13 @@
         <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>491</v>
       </c>
@@ -12171,7 +12159,7 @@
         <v>79</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>80</v>
@@ -12180,15 +12168,17 @@
         <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="M89" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="N89" s="2"/>
+      <c r="N89" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -12213,13 +12203,13 @@
         <v>80</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>80</v>
+        <v>225</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>80</v>
+        <v>495</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>80</v>
+        <v>496</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>80</v>
@@ -12252,13 +12242,13 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>80</v>
+        <v>497</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>80</v>
+        <v>498</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>80</v>
@@ -12266,10 +12256,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12292,16 +12282,16 @@
         <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>225</v>
+        <v>501</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12327,13 +12317,13 @@
         <v>80</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>498</v>
+        <v>80</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>499</v>
+        <v>80</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -12351,7 +12341,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12366,24 +12356,24 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12397,26 +12387,24 @@
         <v>79</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -12465,7 +12453,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12480,28 +12468,28 @@
         <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>502</v>
+        <v>80</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>80</v>
+        <v>514</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12511,7 +12499,7 @@
         <v>79</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>80</v>
@@ -12520,15 +12508,17 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -12577,7 +12567,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12592,10 +12582,10 @@
         <v>100</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>80</v>
@@ -12604,16 +12594,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>517</v>
+        <v>80</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -12623,25 +12613,25 @@
         <v>79</v>
       </c>
       <c r="H93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J93" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K93" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12691,7 +12681,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12706,10 +12696,10 @@
         <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>522</v>
+        <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>80</v>
@@ -12720,14 +12710,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>80</v>
+        <v>528</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -12746,18 +12736,20 @@
         <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>525</v>
+        <v>220</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
       </c>
@@ -12781,13 +12773,13 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>80</v>
+        <v>225</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>80</v>
+        <v>533</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>80</v>
+        <v>534</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -12805,7 +12797,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12823,25 +12815,25 @@
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>80</v>
+        <v>535</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>531</v>
+        <v>80</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -12851,29 +12843,25 @@
         <v>79</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>225</v>
+        <v>537</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>80</v>
       </c>
@@ -12897,31 +12885,31 @@
         <v>80</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12936,24 +12924,24 @@
         <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>80</v>
+        <v>540</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>529</v>
+        <v>407</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12964,25 +12952,25 @@
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J96" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K96" t="s" s="2">
-        <v>540</v>
+        <v>239</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13033,13 +13021,13 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>80</v>
@@ -13048,16 +13036,16 @@
         <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>543</v>
+        <v>80</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>544</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" hidden="true">
@@ -13076,7 +13064,7 @@
         <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>80</v>
@@ -13085,18 +13073,20 @@
         <v>80</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>244</v>
+        <v>546</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>80</v>
@@ -13151,7 +13141,7 @@
         <v>78</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>80</v>
@@ -13160,134 +13150,20 @@
         <v>100</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>80</v>
+        <v>550</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>410</v>
+        <v>217</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O98" s="2"/>
-      <c r="P98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN98" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN98">
+  <autoFilter ref="A1:AN97">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13297,7 +13173,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI97">
+  <conditionalFormatting sqref="A2:AI96">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-therapieempfehlung-nicht-medikamentoes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
